--- a/03_PLANILHAS_CONTROLE/PLANILHA_MESTRA_AGENDA_RESERVADA_OE.xlsx
+++ b/03_PLANILHAS_CONTROLE/PLANILHA_MESTRA_AGENDA_RESERVADA_OE.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agenda Mestre" sheetId="1" r:id="Rdacecd3be6f042ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" r:id="R25f19419a48a4001"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="3" r:id="R7fd487a8f8e94cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agenda Mestre" sheetId="1" r:id="R1d84d44059ed414c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" r:id="Ra6026a2541e7497e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="3" r:id="R9f7dc1a9629f490e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AgendaMestreTable" displayName="AgendaMestreTable" ref="A1:K137" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AgendaMestreTable" displayName="AgendaMestreTable" ref="A1:K134" headerRowCount="1">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Semana"/>
@@ -1454,7 +1454,7 @@
       </x:c>
       <x:c r="H35" s="19" t="str"/>
       <x:c r="I35" s="19" t="str">
-        <x:v>Luiz Guilherme</x:v>
+        <x:v>Letícia Santana</x:v>
       </x:c>
       <x:c r="J35" s="19" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1485,7 +1485,7 @@
       </x:c>
       <x:c r="H36" s="19" t="str"/>
       <x:c r="I36" s="19" t="str">
-        <x:v>Letícia Santana</x:v>
+        <x:v>Everton Renato</x:v>
       </x:c>
       <x:c r="J36" s="19" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1500,10 +1500,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C37" s="19" t="str">
-        <x:v>04/07</x:v>
+        <x:v>05/07</x:v>
       </x:c>
       <x:c r="D37" s="19" t="str">
-        <x:v>Sábado</x:v>
+        <x:v>Domingo</x:v>
       </x:c>
       <x:c r="E37" s="19" t="str">
         <x:v>Bevenutti</x:v>
@@ -1516,7 +1516,7 @@
       </x:c>
       <x:c r="H37" s="19" t="str"/>
       <x:c r="I37" s="19" t="str">
-        <x:v>Everton Renato</x:v>
+        <x:v>Roger Martineli</x:v>
       </x:c>
       <x:c r="J37" s="19" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1547,7 +1547,7 @@
       </x:c>
       <x:c r="H38" s="19" t="str"/>
       <x:c r="I38" s="19" t="str">
-        <x:v>Roger Martineli</x:v>
+        <x:v>Douglas Nunes</x:v>
       </x:c>
       <x:c r="J38" s="19" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1578,7 +1578,7 @@
       </x:c>
       <x:c r="H39" s="19" t="str"/>
       <x:c r="I39" s="19" t="str">
-        <x:v>Douglas Nunes</x:v>
+        <x:v>Nicolas Abreu</x:v>
       </x:c>
       <x:c r="J39" s="19" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1609,7 +1609,7 @@
       </x:c>
       <x:c r="H40" s="19" t="str"/>
       <x:c r="I40" s="19" t="str">
-        <x:v>Nicolas Abreu</x:v>
+        <x:v>Danilo Leite</x:v>
       </x:c>
       <x:c r="J40" s="19" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1640,7 +1640,7 @@
       </x:c>
       <x:c r="H41" s="19" t="str"/>
       <x:c r="I41" s="19" t="str">
-        <x:v>Danilo Leite</x:v>
+        <x:v>Luiz Guilherme</x:v>
       </x:c>
       <x:c r="J41" s="19" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1671,7 +1671,7 @@
       </x:c>
       <x:c r="H42" s="19" t="str"/>
       <x:c r="I42" s="19" t="str">
-        <x:v>Luiz Guilherme</x:v>
+        <x:v>Everton Renato</x:v>
       </x:c>
       <x:c r="J42" s="19" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1679,35 +1679,35 @@
       <x:c r="K42" s="19" t="str"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="19" t="str">
+      <x:c r="A43" s="25" t="str">
         <x:v>AG042</x:v>
       </x:c>
-      <x:c r="B43" s="19" t="str">
-        <x:v>Semana de 29/06 a 05/07</x:v>
-      </x:c>
-      <x:c r="C43" s="19" t="str">
-        <x:v>05/07</x:v>
-      </x:c>
-      <x:c r="D43" s="19" t="str">
-        <x:v>Domingo</x:v>
-      </x:c>
-      <x:c r="E43" s="19" t="str">
-        <x:v>Bevenutti</x:v>
-      </x:c>
-      <x:c r="F43" s="19" t="str">
-        <x:v>Pizzaria Bevenutti</x:v>
-      </x:c>
-      <x:c r="G43" s="19" t="str">
-        <x:v>18h às 00h</x:v>
-      </x:c>
-      <x:c r="H43" s="19" t="str"/>
-      <x:c r="I43" s="19" t="str">
-        <x:v>Everton Renato</x:v>
-      </x:c>
-      <x:c r="J43" s="19" t="str">
-        <x:v>Agenda reservada</x:v>
-      </x:c>
-      <x:c r="K43" s="19" t="str"/>
+      <x:c r="B43" s="25" t="str">
+        <x:v>Semana de 29/06 a 05/07</x:v>
+      </x:c>
+      <x:c r="C43" s="25" t="str">
+        <x:v>29/06</x:v>
+      </x:c>
+      <x:c r="D43" s="25" t="str">
+        <x:v>Segunda-feira</x:v>
+      </x:c>
+      <x:c r="E43" s="25" t="str">
+        <x:v>Fratelli</x:v>
+      </x:c>
+      <x:c r="F43" s="25" t="str">
+        <x:v>Fratelli</x:v>
+      </x:c>
+      <x:c r="G43" s="25" t="str">
+        <x:v>17h às 23h / 18h às 00h</x:v>
+      </x:c>
+      <x:c r="H43" s="25" t="str"/>
+      <x:c r="I43" s="25" t="str">
+        <x:v>Denis Ambrósio</x:v>
+      </x:c>
+      <x:c r="J43" s="25" t="str">
+        <x:v>Agenda reservada</x:v>
+      </x:c>
+      <x:c r="K43" s="25" t="str"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="25" t="str">
@@ -1733,7 +1733,7 @@
       </x:c>
       <x:c r="H44" s="25" t="str"/>
       <x:c r="I44" s="25" t="str">
-        <x:v>Denis Ambrósio</x:v>
+        <x:v>Alexandre Pinheiro</x:v>
       </x:c>
       <x:c r="J44" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1764,7 +1764,7 @@
       </x:c>
       <x:c r="H45" s="25" t="str"/>
       <x:c r="I45" s="25" t="str">
-        <x:v>Alexandre Pinheiro</x:v>
+        <x:v>Gustavo</x:v>
       </x:c>
       <x:c r="J45" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1779,10 +1779,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C46" s="25" t="str">
-        <x:v>29/06</x:v>
+        <x:v>30/06</x:v>
       </x:c>
       <x:c r="D46" s="25" t="str">
-        <x:v>Segunda-feira</x:v>
+        <x:v>Terça-feira</x:v>
       </x:c>
       <x:c r="E46" s="25" t="str">
         <x:v>Fratelli</x:v>
@@ -1795,7 +1795,7 @@
       </x:c>
       <x:c r="H46" s="25" t="str"/>
       <x:c r="I46" s="25" t="str">
-        <x:v>Gustavo</x:v>
+        <x:v>Pedro Henrique</x:v>
       </x:c>
       <x:c r="J46" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1826,7 +1826,7 @@
       </x:c>
       <x:c r="H47" s="25" t="str"/>
       <x:c r="I47" s="25" t="str">
-        <x:v>Pedro Henrique</x:v>
+        <x:v>Alexandre Pinheiro</x:v>
       </x:c>
       <x:c r="J47" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1857,7 +1857,7 @@
       </x:c>
       <x:c r="H48" s="25" t="str"/>
       <x:c r="I48" s="25" t="str">
-        <x:v>Alexandre Pinheiro</x:v>
+        <x:v>Gustavo</x:v>
       </x:c>
       <x:c r="J48" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1872,10 +1872,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C49" s="25" t="str">
-        <x:v>30/06</x:v>
+        <x:v>01/07</x:v>
       </x:c>
       <x:c r="D49" s="25" t="str">
-        <x:v>Terça-feira</x:v>
+        <x:v>Quarta-feira</x:v>
       </x:c>
       <x:c r="E49" s="25" t="str">
         <x:v>Fratelli</x:v>
@@ -1888,7 +1888,7 @@
       </x:c>
       <x:c r="H49" s="25" t="str"/>
       <x:c r="I49" s="25" t="str">
-        <x:v>Gustavo</x:v>
+        <x:v>Pedro Henrique</x:v>
       </x:c>
       <x:c r="J49" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1919,7 +1919,7 @@
       </x:c>
       <x:c r="H50" s="25" t="str"/>
       <x:c r="I50" s="25" t="str">
-        <x:v>Pedro Henrique</x:v>
+        <x:v>Alexandre Pinheiro</x:v>
       </x:c>
       <x:c r="J50" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1950,7 +1950,7 @@
       </x:c>
       <x:c r="H51" s="25" t="str"/>
       <x:c r="I51" s="25" t="str">
-        <x:v>Alexandre Pinheiro</x:v>
+        <x:v>Denis Ambrósio</x:v>
       </x:c>
       <x:c r="J51" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -1965,10 +1965,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C52" s="25" t="str">
-        <x:v>01/07</x:v>
+        <x:v>02/07</x:v>
       </x:c>
       <x:c r="D52" s="25" t="str">
-        <x:v>Quarta-feira</x:v>
+        <x:v>Quinta-feira</x:v>
       </x:c>
       <x:c r="E52" s="25" t="str">
         <x:v>Fratelli</x:v>
@@ -1981,7 +1981,7 @@
       </x:c>
       <x:c r="H52" s="25" t="str"/>
       <x:c r="I52" s="25" t="str">
-        <x:v>Denis Ambrósio</x:v>
+        <x:v>Pedro Henrique</x:v>
       </x:c>
       <x:c r="J52" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2012,7 +2012,7 @@
       </x:c>
       <x:c r="H53" s="25" t="str"/>
       <x:c r="I53" s="25" t="str">
-        <x:v>Pedro Henrique</x:v>
+        <x:v>Alexandre Pinheiro</x:v>
       </x:c>
       <x:c r="J53" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2043,7 +2043,7 @@
       </x:c>
       <x:c r="H54" s="25" t="str"/>
       <x:c r="I54" s="25" t="str">
-        <x:v>Alexandre Pinheiro</x:v>
+        <x:v>Denis Ambrósio</x:v>
       </x:c>
       <x:c r="J54" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2074,7 +2074,7 @@
       </x:c>
       <x:c r="H55" s="25" t="str"/>
       <x:c r="I55" s="25" t="str">
-        <x:v>Denis Ambrósio</x:v>
+        <x:v>Gustavo</x:v>
       </x:c>
       <x:c r="J55" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2089,10 +2089,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C56" s="25" t="str">
-        <x:v>02/07</x:v>
+        <x:v>03/07</x:v>
       </x:c>
       <x:c r="D56" s="25" t="str">
-        <x:v>Quinta-feira</x:v>
+        <x:v>Sexta-feira</x:v>
       </x:c>
       <x:c r="E56" s="25" t="str">
         <x:v>Fratelli</x:v>
@@ -2105,7 +2105,7 @@
       </x:c>
       <x:c r="H56" s="25" t="str"/>
       <x:c r="I56" s="25" t="str">
-        <x:v>Gustavo</x:v>
+        <x:v>Pedro Henrique</x:v>
       </x:c>
       <x:c r="J56" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2136,7 +2136,7 @@
       </x:c>
       <x:c r="H57" s="25" t="str"/>
       <x:c r="I57" s="25" t="str">
-        <x:v>Pedro Henrique</x:v>
+        <x:v>Alexandre Pinheiro</x:v>
       </x:c>
       <x:c r="J57" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2167,7 +2167,7 @@
       </x:c>
       <x:c r="H58" s="25" t="str"/>
       <x:c r="I58" s="25" t="str">
-        <x:v>Alexandre Pinheiro</x:v>
+        <x:v>Denis Ambrósio</x:v>
       </x:c>
       <x:c r="J58" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2198,7 +2198,7 @@
       </x:c>
       <x:c r="H59" s="25" t="str"/>
       <x:c r="I59" s="25" t="str">
-        <x:v>Denis Ambrósio</x:v>
+        <x:v>Gustavo</x:v>
       </x:c>
       <x:c r="J59" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2213,10 +2213,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C60" s="25" t="str">
-        <x:v>03/07</x:v>
+        <x:v>04/07</x:v>
       </x:c>
       <x:c r="D60" s="25" t="str">
-        <x:v>Sexta-feira</x:v>
+        <x:v>Sábado</x:v>
       </x:c>
       <x:c r="E60" s="25" t="str">
         <x:v>Fratelli</x:v>
@@ -2229,7 +2229,7 @@
       </x:c>
       <x:c r="H60" s="25" t="str"/>
       <x:c r="I60" s="25" t="str">
-        <x:v>Gustavo</x:v>
+        <x:v>Pedro Henrique</x:v>
       </x:c>
       <x:c r="J60" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2256,11 +2256,11 @@
         <x:v>Fratelli</x:v>
       </x:c>
       <x:c r="G61" s="25" t="str">
-        <x:v>17h às 23h / 18h às 00h</x:v>
+        <x:v>18h às 00h</x:v>
       </x:c>
       <x:c r="H61" s="25" t="str"/>
       <x:c r="I61" s="25" t="str">
-        <x:v>Pedro Henrique</x:v>
+        <x:v>Luiz Guilherme</x:v>
       </x:c>
       <x:c r="J61" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2291,7 +2291,7 @@
       </x:c>
       <x:c r="H62" s="25" t="str"/>
       <x:c r="I62" s="25" t="str">
-        <x:v>Luiz Guilherme</x:v>
+        <x:v>Denis Ambrósio</x:v>
       </x:c>
       <x:c r="J62" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2322,7 +2322,7 @@
       </x:c>
       <x:c r="H63" s="25" t="str"/>
       <x:c r="I63" s="25" t="str">
-        <x:v>Denis Ambrósio</x:v>
+        <x:v>Gustavo</x:v>
       </x:c>
       <x:c r="J63" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2337,10 +2337,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C64" s="25" t="str">
-        <x:v>04/07</x:v>
+        <x:v>05/07</x:v>
       </x:c>
       <x:c r="D64" s="25" t="str">
-        <x:v>Sábado</x:v>
+        <x:v>Domingo</x:v>
       </x:c>
       <x:c r="E64" s="25" t="str">
         <x:v>Fratelli</x:v>
@@ -2353,7 +2353,7 @@
       </x:c>
       <x:c r="H64" s="25" t="str"/>
       <x:c r="I64" s="25" t="str">
-        <x:v>Gustavo</x:v>
+        <x:v>Pedro Henrique</x:v>
       </x:c>
       <x:c r="J64" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2384,7 +2384,7 @@
       </x:c>
       <x:c r="H65" s="25" t="str"/>
       <x:c r="I65" s="25" t="str">
-        <x:v>Pedro Henrique</x:v>
+        <x:v>Denis Ambrósio</x:v>
       </x:c>
       <x:c r="J65" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2415,7 +2415,7 @@
       </x:c>
       <x:c r="H66" s="25" t="str"/>
       <x:c r="I66" s="25" t="str">
-        <x:v>Denis Ambrósio</x:v>
+        <x:v>Gustavo</x:v>
       </x:c>
       <x:c r="J66" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2446,7 +2446,7 @@
       </x:c>
       <x:c r="H67" s="25" t="str"/>
       <x:c r="I67" s="25" t="str">
-        <x:v>Gustavo</x:v>
+        <x:v>Alexandre Pinheiro</x:v>
       </x:c>
       <x:c r="J67" s="25" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2454,35 +2454,35 @@
       <x:c r="K67" s="25" t="str"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="25" t="str">
+      <x:c r="A68" s="27" t="str">
         <x:v>AG067</x:v>
       </x:c>
-      <x:c r="B68" s="25" t="str">
-        <x:v>Semana de 29/06 a 05/07</x:v>
-      </x:c>
-      <x:c r="C68" s="25" t="str">
-        <x:v>05/07</x:v>
-      </x:c>
-      <x:c r="D68" s="25" t="str">
-        <x:v>Domingo</x:v>
-      </x:c>
-      <x:c r="E68" s="25" t="str">
-        <x:v>Fratelli</x:v>
-      </x:c>
-      <x:c r="F68" s="25" t="str">
-        <x:v>Fratelli</x:v>
-      </x:c>
-      <x:c r="G68" s="25" t="str">
-        <x:v>17h às 23h / 18h às 00h</x:v>
-      </x:c>
-      <x:c r="H68" s="25" t="str"/>
-      <x:c r="I68" s="25" t="str">
-        <x:v>Alexandre Pinheiro</x:v>
-      </x:c>
-      <x:c r="J68" s="25" t="str">
-        <x:v>Agenda reservada</x:v>
-      </x:c>
-      <x:c r="K68" s="25" t="str"/>
+      <x:c r="B68" s="27" t="str">
+        <x:v>Semana de 29/06 a 05/07</x:v>
+      </x:c>
+      <x:c r="C68" s="27" t="str">
+        <x:v>29/06</x:v>
+      </x:c>
+      <x:c r="D68" s="27" t="str">
+        <x:v>Segunda-feira</x:v>
+      </x:c>
+      <x:c r="E68" s="27" t="str">
+        <x:v>Pastel da Drica</x:v>
+      </x:c>
+      <x:c r="F68" s="27" t="str">
+        <x:v>Pastel da Drica</x:v>
+      </x:c>
+      <x:c r="G68" s="27" t="str">
+        <x:v>18h às 00h</x:v>
+      </x:c>
+      <x:c r="H68" s="27" t="str"/>
+      <x:c r="I68" s="27" t="str">
+        <x:v>Luiz Guilherme</x:v>
+      </x:c>
+      <x:c r="J68" s="27" t="str">
+        <x:v>Agenda reservada</x:v>
+      </x:c>
+      <x:c r="K68" s="27" t="str"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="27" t="str">
@@ -2508,7 +2508,7 @@
       </x:c>
       <x:c r="H69" s="27" t="str"/>
       <x:c r="I69" s="27" t="str">
-        <x:v>Luiz Guilherme</x:v>
+        <x:v>Samuel Bauman</x:v>
       </x:c>
       <x:c r="J69" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2539,7 +2539,7 @@
       </x:c>
       <x:c r="H70" s="27" t="str"/>
       <x:c r="I70" s="27" t="str">
-        <x:v>Samuel Bauman</x:v>
+        <x:v>Nicolas Abreu</x:v>
       </x:c>
       <x:c r="J70" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2554,10 +2554,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C71" s="27" t="str">
-        <x:v>29/06</x:v>
+        <x:v>30/06</x:v>
       </x:c>
       <x:c r="D71" s="27" t="str">
-        <x:v>Segunda-feira</x:v>
+        <x:v>Terça-feira</x:v>
       </x:c>
       <x:c r="E71" s="27" t="str">
         <x:v>Pastel da Drica</x:v>
@@ -2570,7 +2570,7 @@
       </x:c>
       <x:c r="H71" s="27" t="str"/>
       <x:c r="I71" s="27" t="str">
-        <x:v>Nicolas Abreu</x:v>
+        <x:v>Reinaldo Alves</x:v>
       </x:c>
       <x:c r="J71" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2601,7 +2601,7 @@
       </x:c>
       <x:c r="H72" s="27" t="str"/>
       <x:c r="I72" s="27" t="str">
-        <x:v>Reinaldo Alves</x:v>
+        <x:v>Samuel Bauman</x:v>
       </x:c>
       <x:c r="J72" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2632,7 +2632,7 @@
       </x:c>
       <x:c r="H73" s="27" t="str"/>
       <x:c r="I73" s="27" t="str">
-        <x:v>Samuel Bauman</x:v>
+        <x:v>Bruno Souza</x:v>
       </x:c>
       <x:c r="J73" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2647,10 +2647,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C74" s="27" t="str">
-        <x:v>30/06</x:v>
+        <x:v>01/07</x:v>
       </x:c>
       <x:c r="D74" s="27" t="str">
-        <x:v>Terça-feira</x:v>
+        <x:v>Quarta-feira</x:v>
       </x:c>
       <x:c r="E74" s="27" t="str">
         <x:v>Pastel da Drica</x:v>
@@ -2663,7 +2663,7 @@
       </x:c>
       <x:c r="H74" s="27" t="str"/>
       <x:c r="I74" s="27" t="str">
-        <x:v>Bruno Souza</x:v>
+        <x:v>Reinaldo Alves</x:v>
       </x:c>
       <x:c r="J74" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2694,7 +2694,7 @@
       </x:c>
       <x:c r="H75" s="27" t="str"/>
       <x:c r="I75" s="27" t="str">
-        <x:v>Reinaldo Alves</x:v>
+        <x:v>Samuel Bauman</x:v>
       </x:c>
       <x:c r="J75" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2725,7 +2725,7 @@
       </x:c>
       <x:c r="H76" s="27" t="str"/>
       <x:c r="I76" s="27" t="str">
-        <x:v>Samuel Bauman</x:v>
+        <x:v>Bruno Souza</x:v>
       </x:c>
       <x:c r="J76" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2740,10 +2740,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C77" s="27" t="str">
-        <x:v>01/07</x:v>
+        <x:v>02/07</x:v>
       </x:c>
       <x:c r="D77" s="27" t="str">
-        <x:v>Quarta-feira</x:v>
+        <x:v>Quinta-feira</x:v>
       </x:c>
       <x:c r="E77" s="27" t="str">
         <x:v>Pastel da Drica</x:v>
@@ -2756,7 +2756,7 @@
       </x:c>
       <x:c r="H77" s="27" t="str"/>
       <x:c r="I77" s="27" t="str">
-        <x:v>Bruno Souza</x:v>
+        <x:v>Reinaldo Alves</x:v>
       </x:c>
       <x:c r="J77" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2787,7 +2787,7 @@
       </x:c>
       <x:c r="H78" s="27" t="str"/>
       <x:c r="I78" s="27" t="str">
-        <x:v>Reinaldo Alves</x:v>
+        <x:v>Samuel Bauman</x:v>
       </x:c>
       <x:c r="J78" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2818,7 +2818,7 @@
       </x:c>
       <x:c r="H79" s="27" t="str"/>
       <x:c r="I79" s="27" t="str">
-        <x:v>Samuel Bauman</x:v>
+        <x:v>Bruno Souza</x:v>
       </x:c>
       <x:c r="J79" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2833,10 +2833,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C80" s="27" t="str">
-        <x:v>02/07</x:v>
+        <x:v>03/07</x:v>
       </x:c>
       <x:c r="D80" s="27" t="str">
-        <x:v>Quinta-feira</x:v>
+        <x:v>Sexta-feira</x:v>
       </x:c>
       <x:c r="E80" s="27" t="str">
         <x:v>Pastel da Drica</x:v>
@@ -2849,7 +2849,7 @@
       </x:c>
       <x:c r="H80" s="27" t="str"/>
       <x:c r="I80" s="27" t="str">
-        <x:v>Bruno Souza</x:v>
+        <x:v>Reinaldo Alves</x:v>
       </x:c>
       <x:c r="J80" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2880,7 +2880,7 @@
       </x:c>
       <x:c r="H81" s="27" t="str"/>
       <x:c r="I81" s="27" t="str">
-        <x:v>Reinaldo Alves</x:v>
+        <x:v>Samuel Bauman</x:v>
       </x:c>
       <x:c r="J81" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2911,7 +2911,7 @@
       </x:c>
       <x:c r="H82" s="27" t="str"/>
       <x:c r="I82" s="27" t="str">
-        <x:v>Samuel Bauman</x:v>
+        <x:v>Bruno Souza</x:v>
       </x:c>
       <x:c r="J82" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2926,10 +2926,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C83" s="27" t="str">
-        <x:v>03/07</x:v>
+        <x:v>04/07</x:v>
       </x:c>
       <x:c r="D83" s="27" t="str">
-        <x:v>Sexta-feira</x:v>
+        <x:v>Sábado</x:v>
       </x:c>
       <x:c r="E83" s="27" t="str">
         <x:v>Pastel da Drica</x:v>
@@ -2942,7 +2942,7 @@
       </x:c>
       <x:c r="H83" s="27" t="str"/>
       <x:c r="I83" s="27" t="str">
-        <x:v>Bruno Souza</x:v>
+        <x:v>Reinaldo Alves</x:v>
       </x:c>
       <x:c r="J83" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -2973,7 +2973,7 @@
       </x:c>
       <x:c r="H84" s="27" t="str"/>
       <x:c r="I84" s="27" t="str">
-        <x:v>Reinaldo Alves</x:v>
+        <x:v>Samuel Bauman</x:v>
       </x:c>
       <x:c r="J84" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3004,7 +3004,7 @@
       </x:c>
       <x:c r="H85" s="27" t="str"/>
       <x:c r="I85" s="27" t="str">
-        <x:v>Samuel Bauman</x:v>
+        <x:v>Bruno Souza</x:v>
       </x:c>
       <x:c r="J85" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3019,10 +3019,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C86" s="27" t="str">
-        <x:v>04/07</x:v>
+        <x:v>05/07</x:v>
       </x:c>
       <x:c r="D86" s="27" t="str">
-        <x:v>Sábado</x:v>
+        <x:v>Domingo</x:v>
       </x:c>
       <x:c r="E86" s="27" t="str">
         <x:v>Pastel da Drica</x:v>
@@ -3035,7 +3035,7 @@
       </x:c>
       <x:c r="H86" s="27" t="str"/>
       <x:c r="I86" s="27" t="str">
-        <x:v>Bruno Souza</x:v>
+        <x:v>Reinaldo Alves</x:v>
       </x:c>
       <x:c r="J86" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3066,7 +3066,7 @@
       </x:c>
       <x:c r="H87" s="27" t="str"/>
       <x:c r="I87" s="27" t="str">
-        <x:v>Reinaldo Alves</x:v>
+        <x:v>Samuel Bauman</x:v>
       </x:c>
       <x:c r="J87" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3097,7 +3097,7 @@
       </x:c>
       <x:c r="H88" s="27" t="str"/>
       <x:c r="I88" s="27" t="str">
-        <x:v>Samuel Bauman</x:v>
+        <x:v>Bruno Souza</x:v>
       </x:c>
       <x:c r="J88" s="27" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3105,35 +3105,35 @@
       <x:c r="K88" s="27" t="str"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="27" t="str">
+      <x:c r="A89" s="29" t="str">
         <x:v>AG088</x:v>
       </x:c>
-      <x:c r="B89" s="27" t="str">
-        <x:v>Semana de 29/06 a 05/07</x:v>
-      </x:c>
-      <x:c r="C89" s="27" t="str">
-        <x:v>05/07</x:v>
-      </x:c>
-      <x:c r="D89" s="27" t="str">
-        <x:v>Domingo</x:v>
-      </x:c>
-      <x:c r="E89" s="27" t="str">
-        <x:v>Pastel da Drica</x:v>
-      </x:c>
-      <x:c r="F89" s="27" t="str">
-        <x:v>Pastel da Drica</x:v>
-      </x:c>
-      <x:c r="G89" s="27" t="str">
-        <x:v>18h às 00h</x:v>
-      </x:c>
-      <x:c r="H89" s="27" t="str"/>
-      <x:c r="I89" s="27" t="str">
-        <x:v>Bruno Souza</x:v>
-      </x:c>
-      <x:c r="J89" s="27" t="str">
-        <x:v>Agenda reservada</x:v>
-      </x:c>
-      <x:c r="K89" s="27" t="str"/>
+      <x:c r="B89" s="29" t="str">
+        <x:v>Semana de 29/06 a 05/07</x:v>
+      </x:c>
+      <x:c r="C89" s="29" t="str">
+        <x:v>30/06</x:v>
+      </x:c>
+      <x:c r="D89" s="29" t="str">
+        <x:v>Terça-feira</x:v>
+      </x:c>
+      <x:c r="E89" s="29" t="str">
+        <x:v>Meridio Pizza</x:v>
+      </x:c>
+      <x:c r="F89" s="29" t="str">
+        <x:v>Meridio Pizza</x:v>
+      </x:c>
+      <x:c r="G89" s="29" t="str">
+        <x:v>18h às 00h</x:v>
+      </x:c>
+      <x:c r="H89" s="29" t="str"/>
+      <x:c r="I89" s="29" t="str">
+        <x:v>Felipe Sousa</x:v>
+      </x:c>
+      <x:c r="J89" s="29" t="str">
+        <x:v>Agenda reservada</x:v>
+      </x:c>
+      <x:c r="K89" s="29" t="str"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="29" t="str">
@@ -3159,7 +3159,7 @@
       </x:c>
       <x:c r="H90" s="29" t="str"/>
       <x:c r="I90" s="29" t="str">
-        <x:v>Felipe Sousa</x:v>
+        <x:v>Guilherme Nunes</x:v>
       </x:c>
       <x:c r="J90" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3190,7 +3190,7 @@
       </x:c>
       <x:c r="H91" s="29" t="str"/>
       <x:c r="I91" s="29" t="str">
-        <x:v>Guilherme Nunes</x:v>
+        <x:v>José Henrique</x:v>
       </x:c>
       <x:c r="J91" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3205,10 +3205,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C92" s="29" t="str">
-        <x:v>30/06</x:v>
+        <x:v>01/07</x:v>
       </x:c>
       <x:c r="D92" s="29" t="str">
-        <x:v>Terça-feira</x:v>
+        <x:v>Quarta-feira</x:v>
       </x:c>
       <x:c r="E92" s="29" t="str">
         <x:v>Meridio Pizza</x:v>
@@ -3221,7 +3221,7 @@
       </x:c>
       <x:c r="H92" s="29" t="str"/>
       <x:c r="I92" s="29" t="str">
-        <x:v>José Henrique</x:v>
+        <x:v>Felipe Sousa</x:v>
       </x:c>
       <x:c r="J92" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3252,7 +3252,7 @@
       </x:c>
       <x:c r="H93" s="29" t="str"/>
       <x:c r="I93" s="29" t="str">
-        <x:v>Felipe Sousa</x:v>
+        <x:v>Guilherme Nunes</x:v>
       </x:c>
       <x:c r="J93" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3283,7 +3283,7 @@
       </x:c>
       <x:c r="H94" s="29" t="str"/>
       <x:c r="I94" s="29" t="str">
-        <x:v>Guilherme Nunes</x:v>
+        <x:v>José Henrique</x:v>
       </x:c>
       <x:c r="J94" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3298,10 +3298,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C95" s="29" t="str">
-        <x:v>01/07</x:v>
+        <x:v>02/07</x:v>
       </x:c>
       <x:c r="D95" s="29" t="str">
-        <x:v>Quarta-feira</x:v>
+        <x:v>Quinta-feira</x:v>
       </x:c>
       <x:c r="E95" s="29" t="str">
         <x:v>Meridio Pizza</x:v>
@@ -3314,7 +3314,7 @@
       </x:c>
       <x:c r="H95" s="29" t="str"/>
       <x:c r="I95" s="29" t="str">
-        <x:v>José Henrique</x:v>
+        <x:v>Felipe Sousa</x:v>
       </x:c>
       <x:c r="J95" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3345,7 +3345,7 @@
       </x:c>
       <x:c r="H96" s="29" t="str"/>
       <x:c r="I96" s="29" t="str">
-        <x:v>Felipe Sousa</x:v>
+        <x:v>Guilherme Nunes</x:v>
       </x:c>
       <x:c r="J96" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3376,7 +3376,7 @@
       </x:c>
       <x:c r="H97" s="29" t="str"/>
       <x:c r="I97" s="29" t="str">
-        <x:v>Guilherme Nunes</x:v>
+        <x:v>José Henrique</x:v>
       </x:c>
       <x:c r="J97" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3391,10 +3391,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C98" s="29" t="str">
-        <x:v>02/07</x:v>
+        <x:v>03/07</x:v>
       </x:c>
       <x:c r="D98" s="29" t="str">
-        <x:v>Quinta-feira</x:v>
+        <x:v>Sexta-feira</x:v>
       </x:c>
       <x:c r="E98" s="29" t="str">
         <x:v>Meridio Pizza</x:v>
@@ -3407,7 +3407,7 @@
       </x:c>
       <x:c r="H98" s="29" t="str"/>
       <x:c r="I98" s="29" t="str">
-        <x:v>José Henrique</x:v>
+        <x:v>Felipe Sousa</x:v>
       </x:c>
       <x:c r="J98" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3438,7 +3438,7 @@
       </x:c>
       <x:c r="H99" s="29" t="str"/>
       <x:c r="I99" s="29" t="str">
-        <x:v>Felipe Sousa</x:v>
+        <x:v>Guilherme Nunes</x:v>
       </x:c>
       <x:c r="J99" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3469,7 +3469,7 @@
       </x:c>
       <x:c r="H100" s="29" t="str"/>
       <x:c r="I100" s="29" t="str">
-        <x:v>Guilherme Nunes</x:v>
+        <x:v>José Henrique</x:v>
       </x:c>
       <x:c r="J100" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3500,7 +3500,7 @@
       </x:c>
       <x:c r="H101" s="29" t="str"/>
       <x:c r="I101" s="29" t="str">
-        <x:v>José Henrique</x:v>
+        <x:v>Flávio</x:v>
       </x:c>
       <x:c r="J101" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3531,7 +3531,7 @@
       </x:c>
       <x:c r="H102" s="29" t="str"/>
       <x:c r="I102" s="29" t="str">
-        <x:v>Flávio</x:v>
+        <x:v>Elton</x:v>
       </x:c>
       <x:c r="J102" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3546,10 +3546,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C103" s="29" t="str">
-        <x:v>03/07</x:v>
+        <x:v>04/07</x:v>
       </x:c>
       <x:c r="D103" s="29" t="str">
-        <x:v>Sexta-feira</x:v>
+        <x:v>Sábado</x:v>
       </x:c>
       <x:c r="E103" s="29" t="str">
         <x:v>Meridio Pizza</x:v>
@@ -3562,7 +3562,7 @@
       </x:c>
       <x:c r="H103" s="29" t="str"/>
       <x:c r="I103" s="29" t="str">
-        <x:v>Elton</x:v>
+        <x:v>Felipe Sousa</x:v>
       </x:c>
       <x:c r="J103" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3593,7 +3593,7 @@
       </x:c>
       <x:c r="H104" s="29" t="str"/>
       <x:c r="I104" s="29" t="str">
-        <x:v>Felipe Sousa</x:v>
+        <x:v>Guilherme Nunes</x:v>
       </x:c>
       <x:c r="J104" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3624,7 +3624,7 @@
       </x:c>
       <x:c r="H105" s="29" t="str"/>
       <x:c r="I105" s="29" t="str">
-        <x:v>Guilherme Nunes</x:v>
+        <x:v>José Henrique</x:v>
       </x:c>
       <x:c r="J105" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3655,7 +3655,7 @@
       </x:c>
       <x:c r="H106" s="29" t="str"/>
       <x:c r="I106" s="29" t="str">
-        <x:v>José Henrique</x:v>
+        <x:v>Flávio</x:v>
       </x:c>
       <x:c r="J106" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3686,7 +3686,7 @@
       </x:c>
       <x:c r="H107" s="29" t="str"/>
       <x:c r="I107" s="29" t="str">
-        <x:v>Flávio</x:v>
+        <x:v>Elton</x:v>
       </x:c>
       <x:c r="J107" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3701,10 +3701,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C108" s="29" t="str">
-        <x:v>04/07</x:v>
+        <x:v>05/07</x:v>
       </x:c>
       <x:c r="D108" s="29" t="str">
-        <x:v>Sábado</x:v>
+        <x:v>Domingo</x:v>
       </x:c>
       <x:c r="E108" s="29" t="str">
         <x:v>Meridio Pizza</x:v>
@@ -3717,7 +3717,7 @@
       </x:c>
       <x:c r="H108" s="29" t="str"/>
       <x:c r="I108" s="29" t="str">
-        <x:v>Elton</x:v>
+        <x:v>Felipe Sousa</x:v>
       </x:c>
       <x:c r="J108" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3748,7 +3748,7 @@
       </x:c>
       <x:c r="H109" s="29" t="str"/>
       <x:c r="I109" s="29" t="str">
-        <x:v>Felipe Sousa</x:v>
+        <x:v>Guilherme Nunes</x:v>
       </x:c>
       <x:c r="J109" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3779,7 +3779,7 @@
       </x:c>
       <x:c r="H110" s="29" t="str"/>
       <x:c r="I110" s="29" t="str">
-        <x:v>Guilherme Nunes</x:v>
+        <x:v>José Henrique</x:v>
       </x:c>
       <x:c r="J110" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3810,7 +3810,7 @@
       </x:c>
       <x:c r="H111" s="29" t="str"/>
       <x:c r="I111" s="29" t="str">
-        <x:v>José Henrique</x:v>
+        <x:v>Flávio</x:v>
       </x:c>
       <x:c r="J111" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3841,7 +3841,7 @@
       </x:c>
       <x:c r="H112" s="29" t="str"/>
       <x:c r="I112" s="29" t="str">
-        <x:v>Flávio</x:v>
+        <x:v>Elton</x:v>
       </x:c>
       <x:c r="J112" s="29" t="str">
         <x:v>Agenda reservada</x:v>
@@ -3849,35 +3849,35 @@
       <x:c r="K112" s="29" t="str"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" s="29" t="str">
+      <x:c r="A113" s="31" t="str">
         <x:v>AG112</x:v>
       </x:c>
-      <x:c r="B113" s="29" t="str">
-        <x:v>Semana de 29/06 a 05/07</x:v>
-      </x:c>
-      <x:c r="C113" s="29" t="str">
-        <x:v>05/07</x:v>
-      </x:c>
-      <x:c r="D113" s="29" t="str">
-        <x:v>Domingo</x:v>
-      </x:c>
-      <x:c r="E113" s="29" t="str">
-        <x:v>Meridio Pizza</x:v>
-      </x:c>
-      <x:c r="F113" s="29" t="str">
-        <x:v>Meridio Pizza</x:v>
-      </x:c>
-      <x:c r="G113" s="29" t="str">
-        <x:v>18h às 00h</x:v>
-      </x:c>
-      <x:c r="H113" s="29" t="str"/>
-      <x:c r="I113" s="29" t="str">
-        <x:v>Elton</x:v>
-      </x:c>
-      <x:c r="J113" s="29" t="str">
-        <x:v>Agenda reservada</x:v>
-      </x:c>
-      <x:c r="K113" s="29" t="str"/>
+      <x:c r="B113" s="31" t="str">
+        <x:v>Semana de 29/06 a 05/07</x:v>
+      </x:c>
+      <x:c r="C113" s="31" t="str">
+        <x:v>29/06</x:v>
+      </x:c>
+      <x:c r="D113" s="31" t="str">
+        <x:v>Segunda-feira</x:v>
+      </x:c>
+      <x:c r="E113" s="31" t="str">
+        <x:v>Barto Restaurante</x:v>
+      </x:c>
+      <x:c r="F113" s="31" t="str">
+        <x:v>Barto Restaurante</x:v>
+      </x:c>
+      <x:c r="G113" s="31" t="str">
+        <x:v>10h45 às 16h45</x:v>
+      </x:c>
+      <x:c r="H113" s="31" t="str"/>
+      <x:c r="I113" s="31" t="str">
+        <x:v>Kaue Alcantara</x:v>
+      </x:c>
+      <x:c r="J113" s="31" t="str">
+        <x:v>Agenda reservada</x:v>
+      </x:c>
+      <x:c r="K113" s="31" t="str"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="31" t="str">
@@ -3887,10 +3887,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C114" s="31" t="str">
-        <x:v>29/06</x:v>
+        <x:v>30/06</x:v>
       </x:c>
       <x:c r="D114" s="31" t="str">
-        <x:v>Segunda-feira</x:v>
+        <x:v>Terça-feira</x:v>
       </x:c>
       <x:c r="E114" s="31" t="str">
         <x:v>Barto Restaurante</x:v>
@@ -3918,10 +3918,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C115" s="31" t="str">
-        <x:v>30/06</x:v>
+        <x:v>01/07</x:v>
       </x:c>
       <x:c r="D115" s="31" t="str">
-        <x:v>Terça-feira</x:v>
+        <x:v>Quarta-feira</x:v>
       </x:c>
       <x:c r="E115" s="31" t="str">
         <x:v>Barto Restaurante</x:v>
@@ -3949,10 +3949,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C116" s="31" t="str">
-        <x:v>01/07</x:v>
+        <x:v>02/07</x:v>
       </x:c>
       <x:c r="D116" s="31" t="str">
-        <x:v>Quarta-feira</x:v>
+        <x:v>Quinta-feira</x:v>
       </x:c>
       <x:c r="E116" s="31" t="str">
         <x:v>Barto Restaurante</x:v>
@@ -3980,10 +3980,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C117" s="31" t="str">
-        <x:v>02/07</x:v>
+        <x:v>03/07</x:v>
       </x:c>
       <x:c r="D117" s="31" t="str">
-        <x:v>Quinta-feira</x:v>
+        <x:v>Sexta-feira</x:v>
       </x:c>
       <x:c r="E117" s="31" t="str">
         <x:v>Barto Restaurante</x:v>
@@ -4011,10 +4011,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C118" s="31" t="str">
-        <x:v>03/07</x:v>
+        <x:v>04/07</x:v>
       </x:c>
       <x:c r="D118" s="31" t="str">
-        <x:v>Sexta-feira</x:v>
+        <x:v>Sábado</x:v>
       </x:c>
       <x:c r="E118" s="31" t="str">
         <x:v>Barto Restaurante</x:v>
@@ -4027,7 +4027,7 @@
       </x:c>
       <x:c r="H118" s="31" t="str"/>
       <x:c r="I118" s="31" t="str">
-        <x:v>Kaue Alcantara</x:v>
+        <x:v>Denilson Silveiro</x:v>
       </x:c>
       <x:c r="J118" s="31" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4042,10 +4042,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C119" s="31" t="str">
-        <x:v>04/07</x:v>
+        <x:v>05/07</x:v>
       </x:c>
       <x:c r="D119" s="31" t="str">
-        <x:v>Sábado</x:v>
+        <x:v>Domingo</x:v>
       </x:c>
       <x:c r="E119" s="31" t="str">
         <x:v>Barto Restaurante</x:v>
@@ -4066,35 +4066,37 @@
       <x:c r="K119" s="31" t="str"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="31" t="str">
+      <x:c r="A120" s="21" t="str">
         <x:v>AG119</x:v>
       </x:c>
-      <x:c r="B120" s="31" t="str">
-        <x:v>Semana de 29/06 a 05/07</x:v>
-      </x:c>
-      <x:c r="C120" s="31" t="str">
-        <x:v>05/07</x:v>
-      </x:c>
-      <x:c r="D120" s="31" t="str">
-        <x:v>Domingo</x:v>
-      </x:c>
-      <x:c r="E120" s="31" t="str">
-        <x:v>Barto Restaurante</x:v>
-      </x:c>
-      <x:c r="F120" s="31" t="str">
-        <x:v>Barto Restaurante</x:v>
-      </x:c>
-      <x:c r="G120" s="31" t="str">
-        <x:v>10h45 às 16h45</x:v>
-      </x:c>
-      <x:c r="H120" s="31" t="str"/>
-      <x:c r="I120" s="31" t="str">
-        <x:v>Denilson Silveiro</x:v>
-      </x:c>
-      <x:c r="J120" s="31" t="str">
-        <x:v>Agenda reservada</x:v>
-      </x:c>
-      <x:c r="K120" s="31" t="str"/>
+      <x:c r="B120" s="21" t="str">
+        <x:v>Semana de 29/06 a 05/07</x:v>
+      </x:c>
+      <x:c r="C120" s="21" t="str">
+        <x:v>30/06</x:v>
+      </x:c>
+      <x:c r="D120" s="21" t="str">
+        <x:v>Terça-feira</x:v>
+      </x:c>
+      <x:c r="E120" s="21" t="str">
+        <x:v>Pastel da Camila</x:v>
+      </x:c>
+      <x:c r="F120" s="21" t="str">
+        <x:v>Pastel da Camila</x:v>
+      </x:c>
+      <x:c r="G120" s="21" t="str">
+        <x:v>10h às 16h</x:v>
+      </x:c>
+      <x:c r="H120" s="21" t="str">
+        <x:v>Turno da manhã</x:v>
+      </x:c>
+      <x:c r="I120" s="21" t="str">
+        <x:v>Luiz Guilherme</x:v>
+      </x:c>
+      <x:c r="J120" s="21" t="str">
+        <x:v>Agenda reservada</x:v>
+      </x:c>
+      <x:c r="K120" s="21" t="str"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="21" t="str">
@@ -4116,13 +4118,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G121" s="21" t="str">
-        <x:v>10h às 16h</x:v>
+        <x:v>16h às 22h</x:v>
       </x:c>
       <x:c r="H121" s="21" t="str">
-        <x:v>Turno da manhã</x:v>
+        <x:v>Turno da tarde</x:v>
       </x:c>
       <x:c r="I121" s="21" t="str">
-        <x:v>Luiz Guilherme</x:v>
+        <x:v>Weslley Santos</x:v>
       </x:c>
       <x:c r="J121" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4137,10 +4139,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C122" s="21" t="str">
-        <x:v>30/06</x:v>
+        <x:v>01/07</x:v>
       </x:c>
       <x:c r="D122" s="21" t="str">
-        <x:v>Terça-feira</x:v>
+        <x:v>Quarta-feira</x:v>
       </x:c>
       <x:c r="E122" s="21" t="str">
         <x:v>Pastel da Camila</x:v>
@@ -4149,13 +4151,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G122" s="21" t="str">
-        <x:v>16h às 22h</x:v>
+        <x:v>10h às 16h</x:v>
       </x:c>
       <x:c r="H122" s="21" t="str">
-        <x:v>Turno da tarde</x:v>
+        <x:v>Turno da manhã</x:v>
       </x:c>
       <x:c r="I122" s="21" t="str">
-        <x:v>Weslley Santos</x:v>
+        <x:v>Luiz Guilherme</x:v>
       </x:c>
       <x:c r="J122" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4182,13 +4184,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G123" s="21" t="str">
-        <x:v>10h às 16h</x:v>
+        <x:v>16h às 22h</x:v>
       </x:c>
       <x:c r="H123" s="21" t="str">
-        <x:v>Turno da manhã</x:v>
+        <x:v>Turno da tarde</x:v>
       </x:c>
       <x:c r="I123" s="21" t="str">
-        <x:v>Luiz Guilherme</x:v>
+        <x:v>Denilson Silveiro</x:v>
       </x:c>
       <x:c r="J123" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4203,10 +4205,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C124" s="21" t="str">
-        <x:v>01/07</x:v>
+        <x:v>02/07</x:v>
       </x:c>
       <x:c r="D124" s="21" t="str">
-        <x:v>Quarta-feira</x:v>
+        <x:v>Quinta-feira</x:v>
       </x:c>
       <x:c r="E124" s="21" t="str">
         <x:v>Pastel da Camila</x:v>
@@ -4215,13 +4217,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G124" s="21" t="str">
-        <x:v>16h às 22h</x:v>
+        <x:v>10h às 16h</x:v>
       </x:c>
       <x:c r="H124" s="21" t="str">
-        <x:v>Turno da tarde</x:v>
+        <x:v>Turno da manhã</x:v>
       </x:c>
       <x:c r="I124" s="21" t="str">
-        <x:v>Denilson Silveiro</x:v>
+        <x:v>Luiz Guilherme</x:v>
       </x:c>
       <x:c r="J124" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4248,13 +4250,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G125" s="21" t="str">
-        <x:v>10h às 16h</x:v>
+        <x:v>16h às 22h</x:v>
       </x:c>
       <x:c r="H125" s="21" t="str">
-        <x:v>Turno da manhã</x:v>
+        <x:v>Turno da tarde</x:v>
       </x:c>
       <x:c r="I125" s="21" t="str">
-        <x:v>Luiz Guilherme</x:v>
+        <x:v>Weslley Santos</x:v>
       </x:c>
       <x:c r="J125" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4269,10 +4271,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C126" s="21" t="str">
-        <x:v>02/07</x:v>
+        <x:v>03/07</x:v>
       </x:c>
       <x:c r="D126" s="21" t="str">
-        <x:v>Quinta-feira</x:v>
+        <x:v>Sexta-feira</x:v>
       </x:c>
       <x:c r="E126" s="21" t="str">
         <x:v>Pastel da Camila</x:v>
@@ -4281,13 +4283,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G126" s="21" t="str">
-        <x:v>16h às 22h</x:v>
+        <x:v>10h às 16h</x:v>
       </x:c>
       <x:c r="H126" s="21" t="str">
-        <x:v>Turno da tarde</x:v>
+        <x:v>Turno da manhã</x:v>
       </x:c>
       <x:c r="I126" s="21" t="str">
-        <x:v>Weslley Santos</x:v>
+        <x:v>Luiz Guilherme</x:v>
       </x:c>
       <x:c r="J126" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4314,13 +4316,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G127" s="21" t="str">
-        <x:v>10h às 16h</x:v>
+        <x:v>16h às 22h</x:v>
       </x:c>
       <x:c r="H127" s="21" t="str">
-        <x:v>Turno da manhã</x:v>
+        <x:v>Turno da tarde</x:v>
       </x:c>
       <x:c r="I127" s="21" t="str">
-        <x:v>Luiz Guilherme</x:v>
+        <x:v>Weslley Santos</x:v>
       </x:c>
       <x:c r="J127" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4353,7 +4355,7 @@
         <x:v>Turno da tarde</x:v>
       </x:c>
       <x:c r="I128" s="21" t="str">
-        <x:v>Weslley Santos</x:v>
+        <x:v>Denilson Silveiro</x:v>
       </x:c>
       <x:c r="J128" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4368,10 +4370,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C129" s="21" t="str">
-        <x:v>03/07</x:v>
+        <x:v>04/07</x:v>
       </x:c>
       <x:c r="D129" s="21" t="str">
-        <x:v>Sexta-feira</x:v>
+        <x:v>Sábado</x:v>
       </x:c>
       <x:c r="E129" s="21" t="str">
         <x:v>Pastel da Camila</x:v>
@@ -4380,13 +4382,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G129" s="21" t="str">
-        <x:v>16h às 22h</x:v>
+        <x:v>10h às 16h</x:v>
       </x:c>
       <x:c r="H129" s="21" t="str">
-        <x:v>Turno da tarde</x:v>
+        <x:v>Turno da manhã</x:v>
       </x:c>
       <x:c r="I129" s="21" t="str">
-        <x:v>Denilson Silveiro</x:v>
+        <x:v>Luiz Guilherme</x:v>
       </x:c>
       <x:c r="J129" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4419,7 +4421,7 @@
         <x:v>Turno da manhã</x:v>
       </x:c>
       <x:c r="I130" s="21" t="str">
-        <x:v>Luiz Guilherme</x:v>
+        <x:v>Lucas Lima</x:v>
       </x:c>
       <x:c r="J130" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4446,13 +4448,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G131" s="21" t="str">
-        <x:v>10h às 16h</x:v>
+        <x:v>16h às 22h</x:v>
       </x:c>
       <x:c r="H131" s="21" t="str">
-        <x:v>Turno da manhã</x:v>
+        <x:v>Turno da tarde</x:v>
       </x:c>
       <x:c r="I131" s="21" t="str">
-        <x:v>Lucas Lima</x:v>
+        <x:v>Weslley Santos</x:v>
       </x:c>
       <x:c r="J131" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4467,10 +4469,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C132" s="21" t="str">
-        <x:v>04/07</x:v>
+        <x:v>05/07</x:v>
       </x:c>
       <x:c r="D132" s="21" t="str">
-        <x:v>Sábado</x:v>
+        <x:v>Domingo</x:v>
       </x:c>
       <x:c r="E132" s="21" t="str">
         <x:v>Pastel da Camila</x:v>
@@ -4479,13 +4481,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G132" s="21" t="str">
-        <x:v>16h às 22h</x:v>
+        <x:v>10h às 16h</x:v>
       </x:c>
       <x:c r="H132" s="21" t="str">
-        <x:v>Turno da tarde</x:v>
+        <x:v>Turno da manhã</x:v>
       </x:c>
       <x:c r="I132" s="21" t="str">
-        <x:v>Weslley Santos</x:v>
+        <x:v>Luiz Guilherme</x:v>
       </x:c>
       <x:c r="J132" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4500,10 +4502,10 @@
         <x:v>Semana de 29/06 a 05/07</x:v>
       </x:c>
       <x:c r="C133" s="21" t="str">
-        <x:v>04/07</x:v>
+        <x:v>05/07</x:v>
       </x:c>
       <x:c r="D133" s="21" t="str">
-        <x:v>Sábado</x:v>
+        <x:v>Domingo</x:v>
       </x:c>
       <x:c r="E133" s="21" t="str">
         <x:v>Pastel da Camila</x:v>
@@ -4512,13 +4514,13 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G133" s="21" t="str">
-        <x:v>16h às 22h</x:v>
+        <x:v>10h às 16h</x:v>
       </x:c>
       <x:c r="H133" s="21" t="str">
-        <x:v>Turno da tarde</x:v>
+        <x:v>Turno da manhã</x:v>
       </x:c>
       <x:c r="I133" s="21" t="str">
-        <x:v>Denilson Silveiro</x:v>
+        <x:v>Lucas Lima</x:v>
       </x:c>
       <x:c r="J133" s="21" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4545,127 +4547,28 @@
         <x:v>Pastel da Camila</x:v>
       </x:c>
       <x:c r="G134" s="21" t="str">
-        <x:v>10h às 16h</x:v>
+        <x:v>16h às 22h</x:v>
       </x:c>
       <x:c r="H134" s="21" t="str">
-        <x:v>Turno da manhã</x:v>
+        <x:v>Turno da tarde</x:v>
       </x:c>
       <x:c r="I134" s="21" t="str">
-        <x:v>Luiz Guilherme</x:v>
+        <x:v>Weslley Santos</x:v>
       </x:c>
       <x:c r="J134" s="21" t="str">
         <x:v>Agenda reservada</x:v>
       </x:c>
       <x:c r="K134" s="21" t="str"/>
-    </x:row>
-    <x:row r="135">
-      <x:c r="A135" s="21" t="str">
-        <x:v>AG134</x:v>
-      </x:c>
-      <x:c r="B135" s="21" t="str">
-        <x:v>Semana de 29/06 a 05/07</x:v>
-      </x:c>
-      <x:c r="C135" s="21" t="str">
-        <x:v>05/07</x:v>
-      </x:c>
-      <x:c r="D135" s="21" t="str">
-        <x:v>Domingo</x:v>
-      </x:c>
-      <x:c r="E135" s="21" t="str">
-        <x:v>Pastel da Camila</x:v>
-      </x:c>
-      <x:c r="F135" s="21" t="str">
-        <x:v>Pastel da Camila</x:v>
-      </x:c>
-      <x:c r="G135" s="21" t="str">
-        <x:v>10h às 16h</x:v>
-      </x:c>
-      <x:c r="H135" s="21" t="str">
-        <x:v>Turno da manhã</x:v>
-      </x:c>
-      <x:c r="I135" s="21" t="str">
-        <x:v>Lucas Lima</x:v>
-      </x:c>
-      <x:c r="J135" s="21" t="str">
-        <x:v>Agenda reservada</x:v>
-      </x:c>
-      <x:c r="K135" s="21" t="str"/>
-    </x:row>
-    <x:row r="136">
-      <x:c r="A136" s="21" t="str">
-        <x:v>AG135</x:v>
-      </x:c>
-      <x:c r="B136" s="21" t="str">
-        <x:v>Semana de 29/06 a 05/07</x:v>
-      </x:c>
-      <x:c r="C136" s="21" t="str">
-        <x:v>05/07</x:v>
-      </x:c>
-      <x:c r="D136" s="21" t="str">
-        <x:v>Domingo</x:v>
-      </x:c>
-      <x:c r="E136" s="21" t="str">
-        <x:v>Pastel da Camila</x:v>
-      </x:c>
-      <x:c r="F136" s="21" t="str">
-        <x:v>Pastel da Camila</x:v>
-      </x:c>
-      <x:c r="G136" s="21" t="str">
-        <x:v>16h às 22h</x:v>
-      </x:c>
-      <x:c r="H136" s="21" t="str">
-        <x:v>Turno da tarde</x:v>
-      </x:c>
-      <x:c r="I136" s="21" t="str">
-        <x:v>Weslley Santos</x:v>
-      </x:c>
-      <x:c r="J136" s="21" t="str">
-        <x:v>Agenda reservada</x:v>
-      </x:c>
-      <x:c r="K136" s="21" t="str"/>
-    </x:row>
-    <x:row r="137">
-      <x:c r="A137" s="21" t="str">
-        <x:v>AG136</x:v>
-      </x:c>
-      <x:c r="B137" s="21" t="str">
-        <x:v>Semana de 29/06 a 05/07</x:v>
-      </x:c>
-      <x:c r="C137" s="21" t="str">
-        <x:v>05/07</x:v>
-      </x:c>
-      <x:c r="D137" s="21" t="str">
-        <x:v>Domingo</x:v>
-      </x:c>
-      <x:c r="E137" s="21" t="str">
-        <x:v>Pastel da Camila</x:v>
-      </x:c>
-      <x:c r="F137" s="21" t="str">
-        <x:v>Pastel da Camila</x:v>
-      </x:c>
-      <x:c r="G137" s="21" t="str">
-        <x:v>16h às 22h</x:v>
-      </x:c>
-      <x:c r="H137" s="21" t="str">
-        <x:v>Turno da tarde</x:v>
-      </x:c>
-      <x:c r="I137" s="21" t="str">
-        <x:v>Denilson Silveiro</x:v>
-      </x:c>
-      <x:c r="J137" s="21" t="str">
-        <x:v>Agenda reservada</x:v>
-      </x:c>
-      <x:c r="K137" s="21" t="str"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="J2:J137">
+    <x:dataValidation type="list" sqref="J2:J134">
       <x:formula1>"Agenda reservada,Vaga aberta,Cancelado"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf313eac242384bb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9280d71a5f384158"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4794,7 +4697,7 @@
       </x:c>
       <x:c r="B3" s="35" t="n">
         <x:f>COUNTIFS('Agenda Mestre'!$E:$E,A3,'Agenda Mestre'!$J:$J,"Agenda reservada")</x:f>
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="35" t="n">
         <x:f>COUNTIFS('Agenda Mestre'!$E:$E,A3,'Agenda Mestre'!$J:$J,"Vaga aberta")</x:f>
@@ -4802,7 +4705,7 @@
       </x:c>
       <x:c r="D3" s="35" t="n">
         <x:f>COUNTIF('Agenda Mestre'!$E:$E,A3)</x:f>
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4845,7 +4748,7 @@
       </x:c>
       <x:c r="B6" s="35" t="n">
         <x:f>COUNTIFS('Agenda Mestre'!$E:$E,A6,'Agenda Mestre'!$J:$J,"Agenda reservada")</x:f>
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="35" t="n">
         <x:f>COUNTIFS('Agenda Mestre'!$E:$E,A6,'Agenda Mestre'!$J:$J,"Vaga aberta")</x:f>
@@ -4853,7 +4756,7 @@
       </x:c>
       <x:c r="D6" s="35" t="n">
         <x:f>COUNTIF('Agenda Mestre'!$E:$E,A6)</x:f>
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7">

--- a/03_PLANILHAS_CONTROLE/PLANILHA_MESTRA_AGENDA_RESERVADA_OE.xlsx
+++ b/03_PLANILHAS_CONTROLE/PLANILHA_MESTRA_AGENDA_RESERVADA_OE.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agenda Mestre" sheetId="1" r:id="R1d84d44059ed414c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" r:id="Ra6026a2541e7497e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="3" r:id="R9f7dc1a9629f490e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agenda Mestre" sheetId="1" r:id="R7ec0e2daa9734d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" r:id="R46120311c46743d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="3" r:id="Ra293c60604f34983"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -431,7 +431,7 @@
       </x:c>
       <x:c r="H2" s="19" t="str"/>
       <x:c r="I2" s="19" t="str">
-        <x:v>Roger Martineli</x:v>
+        <x:v>Douglas Nunes</x:v>
       </x:c>
       <x:c r="J2" s="19" t="str">
         <x:v>Agenda reservada</x:v>
@@ -4568,7 +4568,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9280d71a5f384158"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R368591839ede4f0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
